--- a/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>$411,398.82</t>
+          <t>$456,722.11</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Filed = bank deposits incl non-revenue. Amended = platform-gross basis (Amazon nominee gross + Shopify 1099-K + TikTok platform + other channels)</t>
+          <t>Fix 2 + Fix 3 applied. Filed = bank deposits incl non-revenue. Amended = platform-gross basis: Amazon nominee $224,789 + Shopify 1099-K $109,064 + TikTok $25,417 + Global-E $25,754 + intl wires $7,686 + Kickstarter $54,386 (Fix 2: income) + Amazon CA $6,326 + MX $2,696 + other. BNPL $9,063 removed (Fix 3: inside Shopify 1099-K).</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Owner loans $81,204 + Kickstarter $54,386 EXCLUDED from amended gross. These were inside filed bank-feed but are NOT income.</t>
+          <t>Owner loans $81,204 removed from gross (not income). NOTE: Kickstarter $54,386 MOVED from this exclusion to income (Fix 2). BNPL $9,063 removed as double-count (Fix 3).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Kickstarter $54,386</t>
+          <t>Kickstarter $54,386 — INCOME (Fix 2: cash-basis C-corp)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>DEFERRED (excluded)</t>
+          <t>INCOME — recognized when received</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Unfulfilled as of 12/31/25 — deferred revenue liability on balance sheet. NOT income.</t>
+          <t>Fix 2: Owner decision: SPLT cash-basis C-corp → Kickstarter cash received 2025 = 2025 income. 11 deposits, $54,386.08. Prior "DEFERRED" treatment RETIRED. Fulfillment obligation remains as balance sheet liability. TJ confirm cash-basis for C-corp.</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>$330,884.44</t>
+          <t>$370,235.59</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Amended removes: personal $56,144 + Chase card payments $118,406 (balance sheet) + interco $1,600. Adds: platform fees $100,010 + Chase FB ads $51,295. Net lower.</t>
+          <t>Fix 1 applied: Chase ···3247 non-FB substantiated $39,351 added. Amended removes: personal $56,144 + Chase card payments $118,406 (balance sheet) + interco $1,600. Adds: platform fees $100,010 + Chase FB $51,295 + Chase non-FB $39,351. = Section A $100,010 + Section B $179,580 + Section C $90,646.</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>~$62,883</t>
+          <t>~$68,855</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>⚠️ Amendment RAISES income ~$53K from estimated filed basis. Chase $67K unsubstantiated (key open item). If Chase substantiated: income ~−$4,228 (loss / favorable). See Open Items.</t>
+          <t>FINAL (all 3 fixes applied). = $456,722 gross − $17,631 returns − $370,236 deductions. Fix 1 (Chase $39K deductions) + Fix 2 (Kickstarter $54K income) + Fix 3 (BNPL −$9K) net to +$5,972 vs prior +$62,883. Higher because Kickstarter income outweighs new deductions. Corp tax: ~$14,460 @ 21%. Amendment is COMPLIANCE-DRIVEN (cures 1099-K matching). ⚠️ Could reduce ~$5K if flagged Chase items (CGL $3,195 + Foremost Insur $1,735 etc.) confirmed business.</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Required regardless of tax impact (1099-K matching exposure). Currently +$62,883 income. Chase $67K substantiation = path to breakeven/loss. See Open Items.</t>
+          <t>COMPLIANCE-DRIVEN. Amendment cures 1099-K matching for Amazon (nominee) + Shopify (reported at floor). Final taxable income $68,855 (~$14,460 corp tax). All 3 open items from prior packet now resolved: Chase SUBSTANTIATED, BNPL REMOVED, Kickstarter RECOGNIZED. Remaining TJ items: Shopify Capital interest split; Augusta 14-day verification; COGS method; SGM→SPLT $148K loan-vs-capital.</t>
         </is>
       </c>
     </row>
@@ -886,21 +886,21 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>⚠️  OPEN ITEMS — Must resolve before filing</t>
+          <t>⚠️ REMAINING OPEN ITEMS (TJ + owner — all Chase/BNPL/Kickstarter items now RESOLVED)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>• Chase ~$67K unsubstantiated: Chase 2025 card statements (···3247) NOT in source docs. ~$67K estimated from WF→Chase payments $118,406 minus FB ads $51,295 = residual plug. CANNOT deduct without statements. Pull Chase 2025 and substantiate each charge. If business, reduces amended income $62,883 → ~−$4,228.</t>
+          <t>✅ Chase ···3247 RESOLVED (Fix 1): 9 statements classified, all foot to closing balances. $39,351.15 substantiated non-FB business deductions. FB $51,294.89 separately confirmed (Meta invoice). ⚠️ STILL FLAGGED (owner identification needed before filing): CGL Los Angeles $3,195 (identity unknown — freight/logistics?); Foremost Insurance $1,735 (product liability vs vehicle — std mileage bars vehicle deduction); Paddle.net STOCKLMTS $432 (software?); SW Airlines/LV $186 (business travel?); Unknown FL merchant D24939973 $57; Safety First Driving $475 (personal?). Total flagged: $6,080. If all business: income ~$62,775.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>• BNPL $9,063 + Amazon CA $6,326 + Amazon MX $2,696 — double-count risk: If BNPL ran through Shopify Payments → inside Shopify 1099-K $109,064. If Amazon CA/MX are inside the nominee $224,789.09 computation → already counted. Verify both before final gross receipts. Min gross if all overlap: $393,315.</t>
+          <t>✅ BNPL + Amazon CA/MX RESOLVED (Fix 3): BNPL $9,062.79 REMOVED from gross (confirmed inside Shopify 1099-K per CB 2024 pattern — Affirm/Klarna ran through Shopify Payments on Splitflask store, same platform as CB). Amazon CA $6,325.82 + MX $2,695.74 KEPT (separate marketplace accounts, NOT inside US nominee $224,789.09). ⚠️ TJ: verify if Amazon CA/MX 2025 1099-Ks are on SGM TIN (nominee treatment may also apply).</t>
         </is>
       </c>
     </row>
@@ -1403,25 +1403,25 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>BNPL Splitflask (Affirm/Klarna, WF bank)</t>
+          <t>BNPL (Affirm/Klarna) — REMOVED: inside Shopify 1099-K $109,064</t>
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>9062.790000000001</v>
+        <v>0</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>WF bank deposits</t>
+          <t>REMOVED — double-count</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns REV_BNPL</t>
+          <t>CB 2024 confirmed: Affirm/Klarna runs through Shopify Payments</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>⚠️ DOUBLE-COUNT RISK: If Affirm/BNPL ran through Shopify Payments, this is INSIDE Shopify 1099-K $109,064. If so, REMOVE $9,063 from gross (or gross already captures it). Verify before finalizing.</t>
+          <t>✅ RESOLVED: CB 2024 owner confirmation that Affirm/Klarna ran through Shopify Payments applies to Splitflask Shopify store (same platform). BNPL $9,062.79 is INSIDE Shopify 1099-K $109,064. Removing to prevent double-count. Zero contribution to gross.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>⚠️ DOUBLE-COUNT RISK: If Amazon CA is part of the $224,789.09 nominee computation (same seller account / same SGM 1099-K $240,010 total), it is ALREADY counted above. Remove if confirmed inside nominee.</t>
+          <t>Amazon CA deposits in SPLT WF bank ($0423). NOT inside nominee $224,789.09 (which is US marketplace only, order-date split Feb 5–Dec 31). Amazon CA = separate CA marketplace account. KEEP. ⚠️ TJ verify: if Amazon CA 1099-K is on SGM TIN for 2025, nominee treatment may also apply here (belt-and-suspenders correction; same mechanism as US account).</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>⚠️ Same double-count risk as Amazon CA. Remove if confirmed inside the $240,010 SGM-TIN Amazon 1099-K / nominee figure.</t>
+          <t>Amazon MX deposits in SPLT WF bank ($0423). NOT inside nominee $224,789.09 (US-only). Separate MX marketplace account. KEEP. ⚠️ Same TIN-verification note as Amazon CA.</t>
         </is>
       </c>
     </row>
@@ -1528,27 +1528,25 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>KICKSTARTER $54,386.08 — EXCLUDED (deferred)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
+          <t>Kickstarter pre-orders (11 deposits, SPLT cash received 2025)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>54386.08</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Deferred revenue liability</t>
+          <t>CASH BASIS — INCOME (Fix 2)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns DEFERRED_KICKSTARTER</t>
+          <t>SPLT_2025_Txns DEFERRED_KICKSTARTER → reclassified to income</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>11 deposits, $54,386.08 total. Product NOT fulfilled as of 12/31/25. NOT income — deferred revenue / fulfillment liability on balance sheet. Cash-basis tax treatment TBD by TJ.</t>
+          <t>Fix 2 — Owner decision: SPLT is a cash-basis C-corp. Cash received 2025 = taxable when received. 11 deposits totaling $54,386.08. Product fulfillment timing does not defer income under cash method for a C-corp. ⚠️ TJ confirm cash-basis treatment for C-corp; if accrual method required (C-corps may be required to use accrual if avg annual gross receipts &gt; $30M — not applicable here), revisit. Balance sheet: fulfillment obligation remains as liability. PRIOR note (deferred) RETIRED.</t>
         </is>
       </c>
     </row>
@@ -1556,11 +1554,11 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>TOTAL GROSS RECEIPTS (provisional)</t>
+          <t>TOTAL GROSS RECEIPTS (Fix 2 + Fix 3 applied)</t>
         </is>
       </c>
       <c r="B17" s="21" t="n">
-        <v>411398.82</v>
+        <v>456722.11</v>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
@@ -1572,10 +1570,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ Minimum $393,315 if BNPL $9,063 + Amazon CA $6,326 + Amazon MX $2,696 all confirmed inside Shopify 1099-K / nominee computation and removed.</t>
-        </is>
+      <c r="E17" s="20">
+        <f> Prior $411,398.82 + Kickstarter $54,386.08 (Fix 2, now income) − BNPL $9,062.79 (Fix 3, removed double-count). Amazon CA $6,326 + MX $2,696 KEPT (separate marketplaces, not inside US nominee). Min gross if CA/MX also nominee-overlap: $447,699.</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="8" customHeight="1"/>
@@ -1618,7 +1615,7 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>393767.56</v>
+        <v>439090.85</v>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
@@ -1630,10 +1627,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E21" s="20">
+        <f> Gross $456,722.11 − Amazon returns $17,631.26</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1834,7 +1830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2556,7 +2552,7 @@
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>NON-DEDUCTIBLE items excluded from Section B (in WF bank but removed): PERSONAL $56,144.12 | DEBT_CHASE_PAYMENT $118,405.79 (balance sheet — Chase card CHARGES deducted in Section C, not these payments) | INTERCO_OUT_SGM $1,600.00 (balance sheet) | DEFERRED_KICKSTARTER $54,386.08 (liability) | NON_REV_OWNER_LOAN $81,203.67 (not income) | NON_REV_REVERSAL $6.62</t>
+          <t>NON-DEDUCTIBLE items excluded from Section B (in WF bank but removed): PERSONAL $56,144.12 | DEBT_CHASE_PAYMENT $118,405.79 (balance sheet — Chase card CHARGES deducted in Section C, not these payments) | INTERCO_OUT_SGM $1,600.00 (balance sheet) | NON_REV_OWNER_LOAN $81,203.67 (not income, not expense) | NON_REV_REVERSAL $6.62. Fix 2: DEFERRED_KICKSTARTER $54,386.08 reclassified to INCOME (Tab 3) — removed from this exclusion list; now appears as revenue, not a WF bank exclusion.</t>
         </is>
       </c>
     </row>
@@ -2594,287 +2590,564 @@
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Chase ···3247 non-FB charges (~$67K estimated)</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>DROPPED</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ UNSUBSTANTIATED — DROPPED</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Chase 2025 statements NOT available</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Estimated ~$67,111 from WF→Chase payments $118,406 minus FB ads $51,295 = residual plug. CANNOT deduct without Chase 2025 statements. PULL CHASE 2025 CARD STATEMENTS. If business-verified, this $67K reduces amended income $62,883 → ~−$4,228 (small loss / favorable).</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Veeqo shipping/fulfillment labels (all 9 stmts, Feb–Dec 2025)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>17592</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (9 stmts, all foot)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Per-label shipping charges, hundreds of individual transactions. Shipping fulfillment is core COGS-adjacent cost. Stmts: Chase1–Chase10 (excl Chase7 dup). All statements foot to closing balance.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>SECTION C SUBTOTAL — Chase ···3247 (substantiated only)</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="n">
-        <v>51294.89</v>
-      </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shopify subscriptions + apps (9 stmts)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3844.68</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>⚠️ TJ: verify Shopify Capital repayment split (principal non-deductible, interest deductible). Charges range $12.99–$1,134/month; some may include Shopify Capital payments. Substantiated from card statements; TJ extracts capital vs fee component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Klaviyo email marketing SaaS (9 stmts)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4305</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Email marketing platform. Monthly subscription + usage charges. Nov/Dec had two charges ($385 + $640) = plan upgrade or overage mid-month. All deductible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PatentYogi patent drafting services (Mar, May, Jul stmts)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3942</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (Chase2 $1,707 + Chase6 $362 + Chase4 $1,873)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Patent drafting and prosecution services for Splitflask patent. Deductible as legal/professional fees for IP protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Campaign services: Ecom Filmworks + Crowdfunding Pros + Hugebackers</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3993</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (Chase2, Chase6)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ecom Filmworks $2,000 (video production for Splitflask content). Crowdfunding Pros $1,932 (Kickstarter campaign management). Hugebackers $61 (crowdfunding platform/consulting). All direct Splitflask marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve business card interest (Aug/Sep + Sep/Oct + Oct/Nov)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1314</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Chase stmts Chase1 $377.65 + Chase5 $464.99 + Chase3 $471.40</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Business card interest charged Aug/Sep, Sep/Oct, Oct/Nov statements. Paid in full Feb–Jul 2025 ($0 interest those months). Deductible under IRC §163 as business interest expense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chase Sapphire Reserve annual membership fee</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>550</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chase8 (Feb/Mar 2025 first statement, Fees $550)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Annual credit card membership fee on SPLT business card. Deductible as ordinary business expense. Charged in first statement (card opened Feb 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>IONOS web hosting + domains (all 9 stmts)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>876.5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (multiple charges/month)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IONOS web hosting and domain registration. Monthly recurring service. Chase1 includes PayPal IONOS $323 (likely annual domain renewal). All deductible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Next Insurance — general liability (4 stmts: Aug–Dec)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>411.67</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts Chase1/3/5/9 (~$103/month)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Next Insurance general liability policy for Splitflask. Monthly premium $102.67–$103. Product liability / general commercial coverage. Deductible business insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Fiverr freelance services (Feb/Mar, Mar/Apr, Jun/Jul stmts)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>713</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (Chase8 $449 + Chase2 $198 + Chase4 $66)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Freelance contractors via Fiverr for creative/design/content work. Business purpose: Splitflask product photography, marketing assets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Adv Specialty — promotional/brand materials (Aug/Sep, Sep/Oct)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>596</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Chase stmts Chase1 $298 + Chase5 $298</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Promotional merchandise/materials for Splitflask brand. $298 × 2 statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI tools + SaaS: OpenAI, Claude.ai, QuickBooks, LinkedIn, Reddit/TikTok Ads, GoDaddy + misc</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1723.77</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (itemized in each stmt)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OpenAI ChatGPT $175.01 (AI tool for business). Claude.ai $100 (AI assistant). QuickBooks $50. LinkedIn $45 (professional marketing). Reddit Ads $209. TikTok Ads $120. GoDaddy $133 (domain). Google Workspace $23.76 (flag TJ: Cyberbrands account on SPLT card). DMVerify $14 (mailing list verification). US Patent USPTO $65 (filing fee). AMZ Amazon Payments + Sponsored $134.93. Alibaba $134 (supplies/COGS). Staples $9.60. Hugebackers already above. Total miscellaneous SaaS/tools/ads: $1,723.77.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1"/>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>SECTION C SUBTOTAL — Chase ···3247 (all substantiated, Fix 1 complete)</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="n">
+        <v>90646.03999999999</v>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D54" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E54" s="22">
+        <f> FB ads $51,294.89 + non-FB business $39,351.15. FB: Meta invoice card-coded (SUBSTANTIATED). Non-FB: 9 Chase stmts, all foot to closing balances. Prior "~$67K DROPPED" line RETIRED — now fully substantiated.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL SUBSTANTIATED DEDUCTIONS (Fix 1 applied)</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="n">
+        <v>370235.59</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL SUBSTANTIATED DEDUCTIONS</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="n">
-        <v>330884.44</v>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="3">
-        <f> Section A $100,010 + Section B $179,580 + Section C $51,295</f>
+      <c r="E56" s="3">
+        <f> Section A $100,010 + Section B $179,580 + Section C $90,646</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="8" customHeight="1"/>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>FILED-VS-BANK ANALYSIS</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>Filed gross receipts (estimated)</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>$369,980.87</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>All WF bank credits (bank-feed based)</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Estimated from 3-way match: credits $369,981 − debits $360,131 = closing balance $9,850.39</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>ESTIMATE — TJ must confirm from actual filed 1120</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Filed deductions (UNKNOWN)</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>⚠️ TJ must provide</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Filed 1120 deduction schedule</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>NOT in source docs this session</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>⚠️ CRITICAL: unlike CB 2024 (QB P&amp;L available), no filed deduction detail available. If filed deducted bank debits incl. personal $56K + Chase payments $118K + interco $1.6K → over-deduction $176K (same CB-2024 pattern). TJ provides filed 1120 Part II/III deduction detail.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Filed net income (estimated)</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>~$9,850 est.</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Three-way bank match</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>Credits $369,981 − debits $360,131 = $9,850</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>ESTIMATE only — equals closing bank balance. Real filed taxable income may differ significantly based on actual deductions claimed.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>Amended gross receipts</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>$411,398.82</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>$456,722.11</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Platform-gross basis</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>See Tab 3</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>Increase from filed: Amazon nominee received + TikTok gross + other channels; removal of non-revenue items.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Increase from filed: Amazon nominee + TikTok gross + other channels. Fix 2: Kickstarter $54,386 now income (cash-basis C-corp). Fix 3: BNPL $9,063 removed (inside Shopify 1099-K). Amazon CA/MX kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Amended deductions</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>$330,884.44</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>$370,235.59</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Section A + B + C substantiated</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>See above</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>Adds: platform fees $100K + Chase FB $51K. Removes: personal $56K + Chase payments $118K (balance sheet). Net: lower deductions vs WF-all-debits basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Amended net income (before Chase $67K)</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>~$62,883</t>
-        </is>
-      </c>
-      <c r="C50" s="6">
-        <f> $411,399 − $17,631 returns − $330,884</f>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Fix 1: Chase non-FB $39,351 added (9 stmts, all foot). Adds: platform fees $100K + Chase FB $51K + Chase non-FB $39K. Removes: personal $56K + Chase payments $118K (balance sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Amended net income (FINAL — all 3 fixes applied)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>~$68,855</t>
+        </is>
+      </c>
+      <c r="C64" s="6">
+        <f> $456,722 − $17,631 returns − $370,236</f>
         <v/>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Amendment waterfall</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ Higher than estimated filed $9,850. Chase $67K substantiation = path to ~−$4,228 (small loss). Chase is the key open item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>FINAL: $68,855 taxable income (~$14,460 @ 21% corp rate). Higher than prior +$62,883 because Kickstarter $54,386 added to income (Fix 2) exceeds Chase new deductions $39,351 (Fix 1) net of BNPL removal $9,063 (Fix 3). Delta vs prior: +$54,386 − $39,351 − $9,063 = +$5,972. Still COMPLIANCE-DRIVEN — amendment cures 1099-K matching at proper corporate tax. ⚠️ Flagged Chase items (CGL $3,195 + Foremost Insur $1,735 + Paddle.net $432 + misc) could reduce to ~$63K if owner confirms business purpose. TJ items (Shopify Capital interest) additive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>⚠️ Non-deductibles in WF debits (if filed on bank-feed)</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>$56,144 personal + $118,406 Chase payments + $1,600 interco</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>If filed deducted these</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>WF bank classification</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>If filed return used all bank debits as deductions → over-deduction ~$176K. Amendment corrects by removing these AND adding legitimate platform fees + Chase FB ads. Net effect depends on actual filed numbers — TJ confirms.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -596,6 +596,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -950,6 +951,48 @@
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t>• Corrected Amazon 1099-K from Amazon: Request corrected 1099-K from Amazon under SPLT TIN (EIN 33-3094308) as belt-and-suspenders. Does not change nominee treatment but reduces future inquiry risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>== ASSEMBLY 4C VERIFICATION FINDINGS (2026-07-11) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FB Invoice Reconciliation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Invoice total $97,769.11 CONFIRMED (proper CSV parse). ···3247 $51,294.89 ✓ matches Section C. ···2100 bank $22,351.63 vs invoice $21,216.81 → $1,134.82 flag (Tab 5 note added). No double-count between Sections B and C. CB 2025 FB invoice ($17,818.73 ALL on ···3247) = interco item → Tab 6 updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chase charges-vs-payments</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WF→Chase payments $118,406, Section C charges $90,646. Gap $27,760 = CB interco ads $17,819 + flagged items $6,080 + residual $3,861 (personal/timing). Gap fully explained — no missing SPLT deductions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Final number status</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>+$68,855 CONFIRMED internally consistent. Range: +$62,775 (all 6 flagged Chase items business) to +$69,990 (···2100 $1,134.82 non-Splitflask). Base case $68,855 stands pending owner IDs.</t>
         </is>
       </c>
     </row>
@@ -1854,6 +1897,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2192,7 +2236,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Debit card ···2100 charges IN WF bank statements. SEPARATE from Chase ···3247 credit card in Section C — no double-count.</t>
+          <t>Debit card ···2100 charges IN WF bank statements. SEPARATE from Chase ···3247 credit card in Section C — no double-count. ⚠️ ASSEMBLY 4C FLAG: Bank total $22,351.63 vs Splitflask FB invoice ···2100 $21,216.81 = $1,134.82 delta. Per CLAUDE.md rule, bank is authoritative for debit cards. However, $1,134.82 is NOT on the Splitflask invoice and NOT on the CB invoice (CB invoice = ···3247 only). Owner: confirm which Meta ad account the extra $1,134.82 belongs to (2nd Meta account? period overlap?). If non-Splitflask: remove $1,134.82 → income +$69,990. Currently using bank figure pending ID.</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2629,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Stated from Meta invoice. Card ···3247 = SPLT Chase card. Jan–Mar 2025 = Shark Tank airing period (heavy spend). SEPARATE from WF debit ···2100 (Section B) — no double-count.</t>
+          <t>Stated from Meta invoice. Card ···3247 = SPLT Chase card. Jan–Mar 2025 = Shark Tank airing period (heavy spend). SEPARATE from WF debit ···2100 (Section B) — no double-count. ⚠️ ASSEMBLY 4C FLAG: Bank total $22,351.63 vs Splitflask FB invoice ···2100 $21,216.81 = $1,134.82 delta. Per CLAUDE.md rule, bank is authoritative for debit cards. However, $1,134.82 is NOT on the Splitflask invoice and NOT on the CB invoice (CB invoice = ···3247 only). Owner: confirm which Meta ad account the extra $1,134.82 belongs to (2nd Meta account? period overlap?). If non-Splitflask: remove $1,134.82 → income +$69,990. Currently using bank figure pending ID.</t>
         </is>
       </c>
     </row>
@@ -2890,6 +2934,7 @@
       </c>
     </row>
     <row r="51" ht="42" customHeight="1"/>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="6" t="n"/>
@@ -2921,6 +2966,7 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
@@ -2945,6 +2991,7 @@
         <v/>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
@@ -3159,7 +3206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3182,6 +3229,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -3432,22 +3480,44 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>SPLT↔CB</t>
+          <t>SPLT→CB via Chase ···3247 (NEW — Assembly 4C finding)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>$0 confirmed</t>
+          <t>SPLT paid CB FB ads $17,818.73 via ···3247</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>No interco flows</t>
+          <t>⚠️ INTERCO RECEIVABLE — balance sheet, NOT P&amp;L on SPLT</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Layer 10 verified: zero SPLT↔CB interco transactions in either entity's 2025 statements. PASS.</t>
+          <t>CB 2025 FB invoice (Meta ad account for Cyberbrands) shows ALL $17,818.73 charged to ···3247 (SPLT Chase card). CB paid ZERO of its own FB ads from CB bank. SPLT advanced the payment. Treatment: SPLT records interco receivable $17,818.73 (CB owes SPLT); CB records payable $17,818.73 + FB ad DEDUCTION $17,818.73. Zero P&amp;L impact on SPLT. FEEDS CB 2025 PACKET. Layer 10 SPLT↔CB=$0 was correct for WF bank flows only — Chase card flows were not in scope then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>⚠️ CB 2025 action: deduct $17,818.73 FB ads (paid by SPLT on CB behalf)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$17,818.73</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CB 2025 DEDUCTION — in CB 2025 packet</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Layer 10 was bank-only; Chase card flows discovered in Assembly 4C. CB 2025 packet must add $17,818.73 FB ads from SPLT Chase interco as CB deduction. Cross-check: SPLT receivable $17,818.73 = CB payable $17,818.73.</t>
         </is>
       </c>
     </row>

--- a/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
@@ -596,7 +596,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -786,12 +785,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>$370,235.59</t>
+          <t>$382,529.81</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Fix 1 applied: Chase ···3247 non-FB substantiated $39,351 added. Amended removes: personal $56,144 + Chase card payments $118,406 (balance sheet) + interco $1,600. Adds: platform fees $100,010 + Chase FB $51,295 + Chase non-FB $39,351. = Section A $100,010 + Section B $179,580 + Section C $90,646.</t>
+          <t>Assembly 4D final. Section A $100,010 + Section B $182,724 (adds Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251; removes Paris travel $419) + Section C $99,796 (adds 6 Chase confirmed $6,080 + ···0566 $3,070 = $9,150). Removes: personal $52,999.90 + Chase card payments $118,406 (BS) + interco $1,600 + owner loans $81,204.</t>
         </is>
       </c>
     </row>
@@ -808,12 +807,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>~$68,855</t>
+          <t>~$56,561</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>FINAL (all 3 fixes applied). = $456,722 gross − $17,631 returns − $370,236 deductions. Fix 1 (Chase $39K deductions) + Fix 2 (Kickstarter $54K income) + Fix 3 (BNPL −$9K) net to +$5,972 vs prior +$62,883. Higher because Kickstarter income outweighs new deductions. Corp tax: ~$14,460 @ 21%. Amendment is COMPLIANCE-DRIVEN (cures 1099-K matching). ⚠️ Could reduce ~$5K if flagged Chase items (CGL $3,195 + Foremost Insur $1,735 etc.) confirmed business.</t>
+          <t>ASSEMBLY 4D LOCKED. Gross $456,722 − returns $17,631 − deductions $382,530 = $56,561 taxable income. Corp tax ~$11,878 @ 21%. Amendment is COMPLIANCE-DRIVEN — cures 1099-K matching. Still favorable vs typical outcome because SGM 2024 −$213K pass-through likely offsets on personal return (S-corp). SPLT is a C-corp → C-corp tax owed separately on $56,561.</t>
         </is>
       </c>
     </row>
@@ -894,7 +893,7 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>✅ Chase ···3247 RESOLVED (Fix 1): 9 statements classified, all foot to closing balances. $39,351.15 substantiated non-FB business deductions. FB $51,294.89 separately confirmed (Meta invoice). ⚠️ STILL FLAGGED (owner identification needed before filing): CGL Los Angeles $3,195 (identity unknown — freight/logistics?); Foremost Insurance $1,735 (product liability vs vehicle — std mileage bars vehicle deduction); Paddle.net STOCKLMTS $432 (software?); SW Airlines/LV $186 (business travel?); Unknown FL merchant D24939973 $57; Safety First Driving $475 (personal?). Total flagged: $6,080. If all business: income ~$62,775.</t>
+          <t>✅ ALL CHASE FLAGGED ITEMS RESOLVED (Assembly 4D). Owner confirmed all 6 items + ···0566 as SPLT business. CGL Los Angeles $3,195 = legal expenses. Foremost Insurance $1,735 = PROPERTY insurance (warehouse/premises, NOT vehicle → not barred by std mileage). Paddle.net $432 = software. SW Airlines $186 = business travel LV. FL merchant $57 = business misc. Safety First Driving $475 = business. ···0566 MasterCard $3,070 = SPLT Meta FB ads. Total $9,150 added to Section C. Also: Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251 reclassified from personal to deductible. Paris travel $419 reclassified personal.</t>
         </is>
       </c>
     </row>
@@ -987,12 +986,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Final number status</t>
+          <t>Final number status (Assembly 4D — LOCKED)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>+$68,855 CONFIRMED internally consistent. Range: +$62,775 (all 6 flagged Chase items business) to +$69,990 (···2100 $1,134.82 non-Splitflask). Base case $68,855 stands pending owner IDs.</t>
+          <t>~$56,561 LOCKED. All Chase flagged items confirmed. All personal-bucket reclassifications applied. Paris trip fully in PERSONAL. Tesla stays out (std mileage). ATM stays out (owner draw). ⚠️ Minor further adjustments possible: Shopify Capital interest (additive, lowers profit); COGS method; Foremost = property ins. confirmed. 1099-NEC compliance flag: Venmo influencer payments ≥$600/yr threshold.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1897,7 +1896,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2418,11 +2416,11 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel — business (Las Vegas tradeshow/meeting, Sep 2025)</t>
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>494.24</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
@@ -2431,12 +2429,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_TRAVEL</t>
+          <t>SPLT_2025_Txns OPEX_TRAVEL (LV only: $50.96 hotel + $12.75 airport + $12.00 parking)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Bank-verified. Business purpose documentation required on file.</t>
+          <t>Las Vegas business trip only ($75.71). Paris trip ($418.53: Hotel Villa Saxe $276.61 + Air France $75 + Uber $54.17 + LAX $12.75) REMOVED — owner confirmed Paris = personal. Paris retail ($611.70) was already in PERSONAL.</t>
         </is>
       </c>
     </row>
@@ -2541,206 +2539,201 @@
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Social media advertising — Venmo micro-influencer payments (May–Jul 2025)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1011.65</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns ADS_SOCIAL (19 payments, reclassified 4D)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19 Venmo payments May–Jul 2025, $44–$65 each, total $1,011.65. Shark Tank airing period influencer seeding for Splitflask. Owner confirmed = advertising. ⚠️ TJ: 1099-NEC required if any individual received ≥$600/yr total; filed Sch C said "No" to 1099s — compliance item but does not affect deductibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Boardroom rental reimbursement Q1 2025 (C-corp governance meetings)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns RENT — 4/30/25 transfer, bank memo: "Boardroom Rental Reimbursement Q125" (reclassified 4D)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Owner transfer out $1,000 with explicit bank memo "Boardroom Rental Reimbursement Q125." Deductible rent for C-corp board/governance meetings. Keep meeting minutes on file. Source: S180 4/30/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="8" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Royceton corporate rental (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns RENT — 11/19/25 transfer "Business Checking Balance" (reclassified 4D)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Transfer to Royceton $1,300, bank memo: "Business Checking Balance." Owner confirmed = SPLT warehouse/office rental, deductible. Source: S187 11/19/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Repairs &amp; maintenance — SPLT warehouse electrical (Frank, Sep 2025)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns OPEX_REPAIRS — 2 Zelle payments to Frank 9/17/25 ($185 + $66.10) (reclassified 4D)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Zelle to Frank 9/17/25: $185.00 + $66.10 = $251.10. Owner confirmed = electrician, SPLT warehouse power fix. Repairs &amp; maintenance. Keep invoice on file. Source: S185.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Shopify Capital financing cost (interest portion)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>TJ ITEM</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>⚠️ TJ EXTRACT</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>SPLT_2025_Txns DEBT_SHOPIFY_CAPITAL $4,237.64 total</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Total repaid $4,237.64. Split: PRINCIPAL non-deductible; INTEREST/fee portion = deductible. TJ: pull Shopify Capital agreement to state deductible financing cost. Do NOT deduct the full $4,237.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>SECTION B SUBTOTAL — WF bank (excl. Shopify Capital)</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="n">
-        <v>179579.63</v>
-      </c>
-      <c r="C33" s="22" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>SECTION B SUBTOTAL — WF bank (excl. Shopify Capital; Assembly 4D final)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>182723.85</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="8" customHeight="1"/>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>NON-DEDUCTIBLE items excluded from Section B (in WF bank but removed): PERSONAL $56,144.12 | DEBT_CHASE_PAYMENT $118,405.79 (balance sheet — Chase card CHARGES deducted in Section C, not these payments) | INTERCO_OUT_SGM $1,600.00 (balance sheet) | NON_REV_OWNER_LOAN $81,203.67 (not income, not expense) | NON_REV_REVERSAL $6.62. Fix 2: DEFERRED_KICKSTARTER $54,386.08 reclassified to INCOME (Tab 3) — removed from this exclusion list; now appears as revenue, not a WF bank exclusion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
+    </row>
+    <row r="38" ht="36" customHeight="1"/>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>NON-DEDUCTIBLE items excluded from Section B (in WF bank but removed): PERSONAL $52,999.90 (after 4D reclassifications: Venmo $1,011.65 + Boardroom $1,000 + Royceton $1,300 + Frank $251.10 reclassified OUT; Paris travel $418.53 reclassified IN from OPEX_TRAVEL) | DEBT_CHASE_PAYMENT $118,405.79 (balance sheet) | INTERCO_OUT_SGM $1,600.00 (balance sheet) | NON_REV_OWNER_LOAN $81,203.67 (not income) | NON_REV_REVERSAL $6.62. DEFERRED_KICKSTARTER $54,386.08 = INCOME (Fix 2). Tesla $6,159.15 stays PERSONAL (non-deductible, covered by standard mileage election). ATM cash $1,200 stays PERSONAL (owner draw, no receipt trail). Paris trip all items PERSONAL (retail $611.70 + hotel/flights $418.53 now reclassified here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1"/>
+    <row r="41" ht="8" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>SECTION C — Chase ···3247 Credit Card (charges on Chase, not WF bank)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Facebook ads — Chase ···3247 (stated from Meta invoice, Jan–Mar 2025 heavy)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B42" s="14" t="n">
         <v>51294.89</v>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>Facebook-Ads-Splitflask-2025-invoice (Meta invoice, card-coded)</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Stated from Meta invoice. Card ···3247 = SPLT Chase card. Jan–Mar 2025 = Shark Tank airing period (heavy spend). SEPARATE from WF debit ···2100 (Section B) — no double-count. ⚠️ ASSEMBLY 4C FLAG: Bank total $22,351.63 vs Splitflask FB invoice ···2100 $21,216.81 = $1,134.82 delta. Per CLAUDE.md rule, bank is authoritative for debit cards. However, $1,134.82 is NOT on the Splitflask invoice and NOT on the CB invoice (CB invoice = ···3247 only). Owner: confirm which Meta ad account the extra $1,134.82 belongs to (2nd Meta account? period overlap?). If non-Splitflask: remove $1,134.82 → income +$69,990. Currently using bank figure pending ID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Veeqo shipping/fulfillment labels (all 9 stmts, Feb–Dec 2025)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>17592</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Chase ···3247 stmts (9 stmts, all foot)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Per-label shipping charges, hundreds of individual transactions. Shipping fulfillment is core COGS-adjacent cost. Stmts: Chase1–Chase10 (excl Chase7 dup). All statements foot to closing balance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Shopify subscriptions + apps (9 stmts)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3844.68</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Chase ···3247 stmts</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>⚠️ TJ: verify Shopify Capital repayment split (principal non-deductible, interest deductible). Charges range $12.99–$1,134/month; some may include Shopify Capital payments. Substantiated from card statements; TJ extracts capital vs fee component.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Klaviyo email marketing SaaS (9 stmts)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4305</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Chase ···3247 stmts</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Email marketing platform. Monthly subscription + usage charges. Nov/Dec had two charges ($385 + $640) = plan upgrade or overage mid-month. All deductible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>PatentYogi patent drafting services (Mar, May, Jul stmts)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3942</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Chase ···3247 stmts (Chase2 $1,707 + Chase6 $362 + Chase4 $1,873)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Patent drafting and prosecution services for Splitflask patent. Deductible as legal/professional fees for IP protection.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="8" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Campaign services: Ecom Filmworks + Crowdfunding Pros + Hugebackers</t>
+          <t>Veeqo shipping/fulfillment labels (all 9 stmts, Feb–Dec 2025)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3993</v>
+        <v>17592</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2749,23 +2742,23 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (Chase2, Chase6)</t>
+          <t>Chase ···3247 stmts (9 stmts, all foot)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ecom Filmworks $2,000 (video production for Splitflask content). Crowdfunding Pros $1,932 (Kickstarter campaign management). Hugebackers $61 (crowdfunding platform/consulting). All direct Splitflask marketing.</t>
+          <t>Per-label shipping charges, hundreds of individual transactions. Shipping fulfillment is core COGS-adjacent cost. Stmts: Chase1–Chase10 (excl Chase7 dup). All statements foot to closing balance.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chase Sapphire Reserve business card interest (Aug/Sep + Sep/Oct + Oct/Nov)</t>
+          <t>Shopify subscriptions + apps (9 stmts)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1314</v>
+        <v>3844.68</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2774,23 +2767,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Chase stmts Chase1 $377.65 + Chase5 $464.99 + Chase3 $471.40</t>
+          <t>Chase ···3247 stmts</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Business card interest charged Aug/Sep, Sep/Oct, Oct/Nov statements. Paid in full Feb–Jul 2025 ($0 interest those months). Deductible under IRC §163 as business interest expense.</t>
+          <t>⚠️ TJ: verify Shopify Capital repayment split (principal non-deductible, interest deductible). Charges range $12.99–$1,134/month; some may include Shopify Capital payments. Substantiated from card statements; TJ extracts capital vs fee component.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chase Sapphire Reserve annual membership fee</t>
+          <t>Klaviyo email marketing SaaS (9 stmts)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>550</v>
+        <v>4305</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2799,23 +2792,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Chase8 (Feb/Mar 2025 first statement, Fees $550)</t>
+          <t>Chase ···3247 stmts</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Annual credit card membership fee on SPLT business card. Deductible as ordinary business expense. Charged in first statement (card opened Feb 2025).</t>
+          <t>Email marketing platform. Monthly subscription + usage charges. Nov/Dec had two charges ($385 + $640) = plan upgrade or overage mid-month. All deductible.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IONOS web hosting + domains (all 9 stmts)</t>
+          <t>PatentYogi patent drafting services (Mar, May, Jul stmts)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>876.5</v>
+        <v>3942</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2824,23 +2817,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (multiple charges/month)</t>
+          <t>Chase ···3247 stmts (Chase2 $1,707 + Chase6 $362 + Chase4 $1,873)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IONOS web hosting and domain registration. Monthly recurring service. Chase1 includes PayPal IONOS $323 (likely annual domain renewal). All deductible.</t>
+          <t>Patent drafting and prosecution services for Splitflask patent. Deductible as legal/professional fees for IP protection.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Next Insurance — general liability (4 stmts: Aug–Dec)</t>
+          <t>Campaign services: Ecom Filmworks + Crowdfunding Pros + Hugebackers</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>411.67</v>
+        <v>3993</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2849,23 +2842,23 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts Chase1/3/5/9 (~$103/month)</t>
+          <t>Chase ···3247 stmts (Chase2, Chase6)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Next Insurance general liability policy for Splitflask. Monthly premium $102.67–$103. Product liability / general commercial coverage. Deductible business insurance.</t>
+          <t>Ecom Filmworks $2,000 (video production for Splitflask content). Crowdfunding Pros $1,932 (Kickstarter campaign management). Hugebackers $61 (crowdfunding platform/consulting). All direct Splitflask marketing.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Fiverr freelance services (Feb/Mar, Mar/Apr, Jun/Jul stmts)</t>
+          <t>Chase Sapphire Reserve business card interest (Aug/Sep + Sep/Oct + Oct/Nov)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>713</v>
+        <v>1314</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2874,23 +2867,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (Chase8 $449 + Chase2 $198 + Chase4 $66)</t>
+          <t>Chase stmts Chase1 $377.65 + Chase5 $464.99 + Chase3 $471.40</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Freelance contractors via Fiverr for creative/design/content work. Business purpose: Splitflask product photography, marketing assets.</t>
+          <t>Business card interest charged Aug/Sep, Sep/Oct, Oct/Nov statements. Paid in full Feb–Jul 2025 ($0 interest those months). Deductible under IRC §163 as business interest expense.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Adv Specialty — promotional/brand materials (Aug/Sep, Sep/Oct)</t>
+          <t>Chase Sapphire Reserve annual membership fee</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>596</v>
+        <v>550</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2899,302 +2892,568 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chase stmts Chase1 $298 + Chase5 $298</t>
+          <t>Chase8 (Feb/Mar 2025 first statement, Fees $550)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Promotional merchandise/materials for Splitflask brand. $298 × 2 statements.</t>
+          <t>Annual credit card membership fee on SPLT business card. Deductible as ordinary business expense. Charged in first statement (card opened Feb 2025).</t>
         </is>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
+          <t>IONOS web hosting + domains (all 9 stmts)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>876.5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (multiple charges/month)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>IONOS web hosting and domain registration. Monthly recurring service. Chase1 includes PayPal IONOS $323 (likely annual domain renewal). All deductible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Next Insurance — general liability (4 stmts: Aug–Dec)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>411.67</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts Chase1/3/5/9 (~$103/month)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Next Insurance general liability policy for Splitflask. Monthly premium $102.67–$103. Product liability / general commercial coverage. Deductible business insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fiverr freelance services (Feb/Mar, Mar/Apr, Jun/Jul stmts)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>713</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts (Chase8 $449 + Chase2 $198 + Chase4 $66)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Freelance contractors via Fiverr for creative/design/content work. Business purpose: Splitflask product photography, marketing assets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Adv Specialty — promotional/brand materials (Aug/Sep, Sep/Oct)</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>596</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Chase stmts Chase1 $298 + Chase5 $298</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Promotional merchandise/materials for Splitflask brand. $298 × 2 statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>AI tools + SaaS: OpenAI, Claude.ai, QuickBooks, LinkedIn, Reddit/TikTok Ads, GoDaddy + misc</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B54" t="n">
         <v>1723.77</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Chase ···3247 stmts (itemized in each stmt)</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>OpenAI ChatGPT $175.01 (AI tool for business). Claude.ai $100 (AI assistant). QuickBooks $50. LinkedIn $45 (professional marketing). Reddit Ads $209. TikTok Ads $120. GoDaddy $133 (domain). Google Workspace $23.76 (flag TJ: Cyberbrands account on SPLT card). DMVerify $14 (mailing list verification). US Patent USPTO $65 (filing fee). AMZ Amazon Payments + Sponsored $134.93. Alibaba $134 (supplies/COGS). Staples $9.60. Hugebackers already above. Total miscellaneous SaaS/tools/ads: $1,723.77.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="42" customHeight="1"/>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>SECTION C SUBTOTAL — Chase ···3247 (all substantiated, Fix 1 complete)</t>
-        </is>
-      </c>
-      <c r="B54" s="23" t="n">
-        <v>90646.03999999999</v>
-      </c>
-      <c r="C54" s="22" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CGL Los Angeles — legal/logistics services</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3195</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmts Chase8 $2,775 + Chase2 $420 (4D: owner confirmed business)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CGL Los Angeles. Owner confirmed = SPLT legal expenses (formation/contracts/IP). Two charges: Chase8 $2,775 + Chase2 $420 = $3,195. Deductible as legal/professional fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Foremost Insurance — property/warehouse insurance</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1735</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmt Chase2 (4D: confirmed PROPERTY insurance, not vehicle)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Foremost Insurance $1,735. RESOLVED: property/warehouse/premises insurance, NOT vehicle insurance. Standard mileage bar does NOT apply. Deductible as business insurance. Source: Chase2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Paddle.net STOCKLMTS — software subscription</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>432</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmt Chase6 (4D: owner confirmed business software)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Paddle.net STOCKLMTS $432. Owner confirmed = business software subscription. Deductible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SW Airlines — business travel (Las Vegas, business purpose)</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>186</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmt Chase2 (4D: owner confirmed business travel)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SW Airlines Las Vegas $186. Owner confirmed business trip (tradeshow/supplier/meeting). Deductible travel. Document business purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Merchant D24939973 FL — misc business expense</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmt Chase4 (4D: owner confirmed business)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Unknown FL merchant D24939973 $57. Owner confirmed = SPLT business expense. Deductible. Owner to identify vendor for records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Safety First Driving — business safety training</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>475</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmt Chase6 (4D: owner confirmed business)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Safety First Driving $475. Owner confirmed = SPLT business expense (safety training/certification). Deductible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Facebook ads — Meta ···0566 MasterCard (SPLT expense)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3070</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Meta FB invoice 2025, card ···0566 MasterCard (4D: owner confirmed SPLT expense)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>···0566 MasterCard $3,069.79 ≈ $3,070. Identified from Meta FB invoice 2025. Owner confirmed = SPLT advertising expense. Source: Facebook-Ads-Splitflask-2025-invoice card ···0566. ⚠️ TJ: confirm ···0566 card identity and ensure bank statement from that card is on file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>SECTION C SUBTOTAL — Chase ···3247 + ···0566 confirmed (Assembly 4D final)</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="n">
+        <v>99796.03999999999</v>
+      </c>
+      <c r="C65" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D54" s="22" t="inlineStr">
+      <c r="D65" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="22">
+      <c r="E65" s="22">
         <f> FB ads $51,294.89 + non-FB business $39,351.15. FB: Meta invoice card-coded (SUBSTANTIATED). Non-FB: 9 Chase stmts, all foot to closing balances. Prior "~$67K DROPPED" line RETIRED — now fully substantiated.</f>
         <v/>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL SUBSTANTIATED DEDUCTIONS (Fix 1 applied)</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="n">
-        <v>370235.59</v>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL SUBSTANTIATED DEDUCTIONS (Assembly 4D — LOCKED FINAL)</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>382529.81</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E56" s="3">
+      <c r="E67" s="3">
         <f> Section A $100,010 + Section B $179,580 + Section C $90,646</f>
         <v/>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="22" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
         <is>
           <t>FILED-VS-BANK ANALYSIS</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>Filed gross receipts (estimated)</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>$369,980.87</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>All WF bank credits (bank-feed based)</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Estimated from 3-way match: credits $369,981 − debits $360,131 = closing balance $9,850.39</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>ESTIMATE — TJ must confirm from actual filed 1120</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Filed deductions (UNKNOWN)</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>⚠️ TJ must provide</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Filed 1120 deduction schedule</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>NOT in source docs this session</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>⚠️ CRITICAL: unlike CB 2024 (QB P&amp;L available), no filed deduction detail available. If filed deducted bank debits incl. personal $56K + Chase payments $118K + interco $1.6K → over-deduction $176K (same CB-2024 pattern). TJ provides filed 1120 Part II/III deduction detail.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>Filed net income (estimated)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>~$9,850 est.</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Three-way bank match</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Credits $369,981 − debits $360,131 = $9,850</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>ESTIMATE only — equals closing bank balance. Real filed taxable income may differ significantly based on actual deductions claimed.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>Amended gross receipts</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>$456,722.11</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Platform-gross basis</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>See Tab 3</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>Increase from filed: Amazon nominee + TikTok gross + other channels. Fix 2: Kickstarter $54,386 now income (cash-basis C-corp). Fix 3: BNPL $9,063 removed (inside Shopify 1099-K). Amazon CA/MX kept.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>Amended deductions</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>$370,235.59</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>Section A + B + C substantiated</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>$382,529.81</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Assembly 4D final — Section B +$3,144 + Section C +$9,150 = +$12,294 new deductions</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>See above</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>Fix 1: Chase non-FB $39,351 added (9 stmts, all foot). Adds: platform fees $100K + Chase FB $51K + Chase non-FB $39K. Removes: personal $56K + Chase payments $118K (balance sheet).</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Amended net income (FINAL — all 3 fixes applied)</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>~$68,855</t>
-        </is>
-      </c>
-      <c r="C64" s="6">
-        <f> $456,722 − $17,631 returns − $370,236</f>
-        <v/>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Amended net income (FINAL — Assembly 4D LOCKED)</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>~$56,561</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Amendment waterfall</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>FINAL: $68,855 taxable income (~$14,460 @ 21% corp rate). Higher than prior +$62,883 because Kickstarter $54,386 added to income (Fix 2) exceeds Chase new deductions $39,351 (Fix 1) net of BNPL removal $9,063 (Fix 3). Delta vs prior: +$54,386 − $39,351 − $9,063 = +$5,972. Still COMPLIANCE-DRIVEN — amendment cures 1099-K matching at proper corporate tax. ⚠️ Flagged Chase items (CGL $3,195 + Foremost Insur $1,735 + Paddle.net $432 + misc) could reduce to ~$63K if owner confirms business purpose. TJ items (Shopify Capital interest) additive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>ASSEMBLY 4D LOCKED: $56,561 (~$11,878 @ 21% corp rate). Waterfall from Assembly 4C: $68,855 (base) → −$6,080 (6 Chase flagged items confirmed business) → −$3,070 (···0566 confirmed SPLT) → −$3,144 (personal-bucket reclassifications: Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251; net of Paris travel $419 removed). = $56,561. Corp tax: ~$11,878 @ 21%. Still COMPLIANCE-DRIVEN. ⚠️ TJ items: Shopify Capital interest (additive, lowers profit further); COGS method; Augusta 14-day cap; $148K loan-vs-capital. ⚠️ 1099-NEC: Venmo influencer payments (19 × $44–$65 = $1,012) — confirm no individual ≥$600/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>⚠️ Non-deductibles in WF debits (if filed on bank-feed)</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>$56,144 personal + $118,406 Chase payments + $1,600 interco</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>If filed deducted these</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>WF bank classification</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>If filed return used all bank debits as deductions → over-deduction ~$176K. Amendment corrects by removing these AND adding legitimate platform fees + Chase FB ads. Net effect depends on actual filed numbers — TJ confirms.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A35:E35"/>
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3229,7 +3488,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
         <is>

--- a/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
@@ -596,6 +596,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -719,7 +720,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>$(77,433.29)</t>
+          <t>$(76,485.63)</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -953,6 +954,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29">
         <f>== ASSEMBLY 4C VERIFICATION FINDINGS (2026-07-11) ===</f>
@@ -1896,6 +1898,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2012,7 +2015,7 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>4886</v>
+        <v>3938.34</v>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
@@ -3201,6 +3204,8 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="6" t="n"/>
       <c r="B64" s="6" t="n"/>
@@ -3232,6 +3237,7 @@
         <v/>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
@@ -3256,6 +3262,7 @@
         <v/>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
@@ -3488,6 +3495,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -3564,7 +3572,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>-77433.28999999999</v>
+        <v>-76485.62999999999</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
@@ -3573,7 +3581,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Fees on the nominee portion are deducted by SPLT, not SGM. SGM deducts only its Jan 1–Feb 4 slice ($7,071). Total SPLT Amazon fees $77,433.29 (stated, S339). Coherence check confirmed (26.7% blended, not inflated).</t>
+          <t>Fees on the nominee portion are deducted by SPLT, not SGM. SGM deducts only its Jan 1–Feb 4 slice ($7,071). Total SPLT Amazon fees $76,485.63 (stated, S339). Coherence check confirmed (26.7% blended, not inflated).</t>
         </is>
       </c>
     </row>

--- a/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
@@ -786,12 +786,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>$382,529.81</t>
+          <t>$385,273.88</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Assembly 4D final. Section A $100,010 + Section B $182,724 (adds Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251; removes Paris travel $419) + Section C $99,796 (adds 6 Chase confirmed $6,080 + ···0566 $3,070 = $9,150). Removes: personal $52,999.90 + Chase card payments $118,406 (BS) + interco $1,600 + owner loans $81,204.</t>
+          <t>Assembly 4D final. Section A $100,010 + Section B $182,724 (adds Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251; removes Paris travel $419) + Section C $99,796 (adds 6 Chase confirmed $6,080 + ···0566 $3,070 = $9,150). Removes: personal $52,999.90 + Chase card payments $118,406 (BS) + interco $1,600 + owner loans $81,204. FIX 1: +intl Amazon ads $2,319.20 + misc Amazon fees $424.87 = +$2,744.07 new deductions. Was $382,529.81.</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>~$56,561</t>
+          <t>~$53,817</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>ASSEMBLY 4D LOCKED. Gross $456,722 − returns $17,631 − deductions $382,530 = $56,561 taxable income. Corp tax ~$11,878 @ 21%. Amendment is COMPLIANCE-DRIVEN — cures 1099-K matching. Still favorable vs typical outcome because SGM 2024 −$213K pass-through likely offsets on personal return (S-corp). SPLT is a C-corp → C-corp tax owed separately on $56,561.</t>
+          <t>FIX 1 applied: Assembly 4D $56,561 − intl Amazon ads $2,319 − misc Amazon fees $425 = $53,817. C-corp tax ~$11,302 @ 21%.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1898,7 +1898,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2109,121 +2108,103 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>International Amazon ads (MX/CA/AUD, 2025 — billed in local currency)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2319.2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Splitflask-AMA Ad_Spend_2025.csv. MXN 2,394.44 × 0.0503 = $120.44 + CAD 3,025.58 × 0.7241 = $2,190.82 + AUD 12.48 × 0.6361 = $7.94. FX: 2025 avg IRS rates (MXN 19.88/USD; CAD 1.381/USD; AUD 1.572/USD). Ad periods: MXN Jan–Dec 2025; CAD Jan–Nov 2025; AUD Oct–Dec 2025. NOT in US settlement (S339) — billed through MX/CA/AU accounts. PURE EXPENSE per owner.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FIX 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Misc Amazon fees: FBA Transaction fees + Amazon Fees − Adjustments (SPLT period Feb 5–Dec 31)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>424.87</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Splitflask-AMA 2025Jan1-2025Dec31CustomUnifiedTransaction.csv. FBA Transaction fees (SPLT period proportional) $533.93 + Amazon Fees (type "Amazon Fees") $167.06 − Adjustments $276.12 = $424.87. Stated from unified transaction CSV.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FIX 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>SECTION A SUBTOTAL — Platform fees</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
-        <v>100009.92</v>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+    </row>
+    <row r="16" ht="36" customHeight="1"/>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>SECTION B — WF Bank Deductions (SPLT_2025_Txns, all 12 months footed, closing balance $9,850.39)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>COGS — supplier payments (Kangdao / Dongguan)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B18" s="14" t="n">
         <v>103463</v>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>SPLT_2025_Txns COGS_SUPPLIER</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>See Tab 4 for cash vs inventory method options. TJ confirms method.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Freight / logistics</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>18235</v>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>SPLT_2025_Txns FREIGHT</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Third-party logistics payments, bank-verified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Rent — Augusta Rule</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>20500</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ TJ CONFIRM</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>SPLT_2025_Txns RENT</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Bank-substantiated. ⚠️ 14-day cap required; no home-office double-stack. TJ confirms days + FMR documentation.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Facebook ads — WF bank debit card ···2100 (IN bank)</t>
+          <t>Freight / logistics</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>22351.63</v>
+        <v>18235</v>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
@@ -2232,48 +2213,48 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns ADS_FACEBOOK</t>
+          <t>SPLT_2025_Txns FREIGHT</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Debit card ···2100 charges IN WF bank statements. SEPARATE from Chase ···3247 credit card in Section C — no double-count. ⚠️ ASSEMBLY 4C FLAG: Bank total $22,351.63 vs Splitflask FB invoice ···2100 $21,216.81 = $1,134.82 delta. Per CLAUDE.md rule, bank is authoritative for debit cards. However, $1,134.82 is NOT on the Splitflask invoice and NOT on the CB invoice (CB invoice = ···3247 only). Owner: confirm which Meta ad account the extra $1,134.82 belongs to (2nd Meta account? period overlap?). If non-Splitflask: remove $1,134.82 → income +$69,990. Currently using bank figure pending ID.</t>
+          <t>Third-party logistics payments, bank-verified.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Google ads</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n">
-        <v>497.77</v>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>SPLT_2025_Txns ADS_GOOGLE</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Bank-verified.</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Rent — Augusta Rule</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>20500</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ TJ CONFIRM</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns RENT</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Bank-substantiated. ⚠️ 14-day cap required; no home-office double-stack. TJ confirms days + FMR documentation.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Contractor / freelance</t>
+          <t>Facebook ads — WF bank debit card ···2100 (IN bank)</t>
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>2035.47</v>
+        <v>22351.63</v>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
@@ -2282,23 +2263,23 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_CONTRACTOR</t>
+          <t>SPLT_2025_Txns ADS_FACEBOOK</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Bank-verified.</t>
+          <t>Debit card ···2100 charges IN WF bank statements. SEPARATE from Chase ···3247 credit card in Section C — no double-count. ⚠️ ASSEMBLY 4C FLAG: Bank total $22,351.63 vs Splitflask FB invoice ···2100 $21,216.81 = $1,134.82 delta. Per CLAUDE.md rule, bank is authoritative for debit cards. However, $1,134.82 is NOT on the Splitflask invoice and NOT on the CB invoice (CB invoice = ···3247 only). Owner: confirm which Meta ad account the extra $1,134.82 belongs to (2nd Meta account? period overlap?). If non-Splitflask: remove $1,134.82 → income +$69,990. Currently using bank figure pending ID.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Legal / patent</t>
+          <t>Google ads</t>
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>2538</v>
+        <v>497.77</v>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
@@ -2307,7 +2288,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_LEGAL_PATENT</t>
+          <t>SPLT_2025_Txns ADS_GOOGLE</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -2319,11 +2300,11 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Platform fees / subscriptions (bank-direct)</t>
+          <t>Contractor / freelance</t>
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>3591.37</v>
+        <v>2035.47</v>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
@@ -2332,23 +2313,23 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_PLATFORM_FEE</t>
+          <t>SPLT_2025_Txns OPEX_CONTRACTOR</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Shopify subscription, other SaaS subscriptions. Distinct from Shopify Payments fee (Section A).</t>
+          <t>Bank-verified.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Shipping (non-freight, outbound)</t>
+          <t>Legal / patent</t>
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>364.06</v>
+        <v>2538</v>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
@@ -2357,7 +2338,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_SHIPPING</t>
+          <t>SPLT_2025_Txns OPEX_LEGAL_PATENT</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -2369,11 +2350,11 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Platform fees / subscriptions (bank-direct)</t>
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>2002.15</v>
+        <v>3591.37</v>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
@@ -2382,23 +2363,23 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_SOFTWARE</t>
+          <t>SPLT_2025_Txns OPEX_PLATFORM_FEE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Bank-verified.</t>
+          <t>Shopify subscription, other SaaS subscriptions. Distinct from Shopify Payments fee (Section A).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Shipping (non-freight, outbound)</t>
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>2364.67</v>
+        <v>364.06</v>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
@@ -2407,7 +2388,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_SUPPLIES</t>
+          <t>SPLT_2025_Txns OPEX_SHIPPING</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -2419,11 +2400,11 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Travel — business (Las Vegas tradeshow/meeting, Sep 2025)</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>75.70999999999999</v>
+        <v>2002.15</v>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
@@ -2432,23 +2413,23 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_TRAVEL (LV only: $50.96 hotel + $12.75 airport + $12.00 parking)</t>
+          <t>SPLT_2025_Txns OPEX_SOFTWARE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Las Vegas business trip only ($75.71). Paris trip ($418.53: Hotel Villa Saxe $276.61 + Air France $75 + Uber $54.17 + LAX $12.75) REMOVED — owner confirmed Paris = personal. Paris retail ($611.70) was already in PERSONAL.</t>
+          <t>Bank-verified.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Other operating expenses</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>388.49</v>
+        <v>2364.67</v>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
@@ -2457,23 +2438,23 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns OPEX_OTHER</t>
+          <t>SPLT_2025_Txns OPEX_SUPPLIES</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Miscellaneous bank-verified business expenses.</t>
+          <t>Bank-verified.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Bank fees (WF service charges)</t>
+          <t>Travel — business (Las Vegas tradeshow/meeting, Sep 2025)</t>
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>498.78</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
@@ -2482,123 +2463,123 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns BANK_FEE</t>
+          <t>SPLT_2025_Txns OPEX_TRAVEL (LV only: $50.96 hotel + $12.75 airport + $12.00 parking)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Bank-verified.</t>
+          <t>Las Vegas business trip only ($75.71). Paris trip ($418.53: Hotel Villa Saxe $276.61 + Air France $75 + Uber $54.17 + LAX $12.75) REMOVED — owner confirmed Paris = personal. Paris retail ($611.70) was already in PERSONAL.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Meals (50% haircut applied: $163.30 × 50%)</t>
+          <t>Other operating expenses</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>81.65000000000001</v>
+        <v>388.49</v>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>SUBSTANTIATED (50%)</t>
+          <t>SUBSTANTIATED</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns MEALS</t>
+          <t>SPLT_2025_Txns OPEX_OTHER</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Gross $163.30; deductible 50% = $81.65. Business purpose required.</t>
+          <t>Miscellaneous bank-verified business expenses.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
+          <t>Bank fees (WF service charges)</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>498.78</v>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns BANK_FEE</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Bank-verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Meals (50% haircut applied: $163.30 × 50%)</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>81.65000000000001</v>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (50%)</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns MEALS</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Gross $163.30; deductible 50% = $81.65. Business purpose required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
           <t>State / franchise taxes paid</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B33" s="14" t="n">
         <v>255</v>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>SPLT_2025_Txns TAX_PAYMENT</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Bank-verified state tax payments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Social media advertising — Venmo micro-influencer payments (May–Jul 2025)</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1011.65</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SPLT_2025_Txns ADS_SOCIAL (19 payments, reclassified 4D)</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>19 Venmo payments May–Jul 2025, $44–$65 each, total $1,011.65. Shark Tank airing period influencer seeding for Splitflask. Owner confirmed = advertising. ⚠️ TJ: 1099-NEC required if any individual received ≥$600/yr total; filed Sch C said "No" to 1099s — compliance item but does not affect deductibility.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Boardroom rental reimbursement Q1 2025 (C-corp governance meetings)</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SPLT_2025_Txns RENT — 4/30/25 transfer, bank memo: "Boardroom Rental Reimbursement Q125" (reclassified 4D)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Owner transfer out $1,000 with explicit bank memo "Boardroom Rental Reimbursement Q125." Deductible rent for C-corp board/governance meetings. Keep meeting minutes on file. Source: S180 4/30/25.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="8" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Royceton corporate rental (Nov 2025)</t>
+          <t>Social media advertising — Venmo micro-influencer payments (May–Jul 2025)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1300</v>
+        <v>1011.65</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2607,186 +2588,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SPLT_2025_Txns RENT — 11/19/25 transfer "Business Checking Balance" (reclassified 4D)</t>
+          <t>SPLT_2025_Txns ADS_SOCIAL (19 payments, reclassified 4D)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Transfer to Royceton $1,300, bank memo: "Business Checking Balance." Owner confirmed = SPLT warehouse/office rental, deductible. Source: S187 11/19/25.</t>
+          <t>19 Venmo payments May–Jul 2025, $44–$65 each, total $1,011.65. Shark Tank airing period influencer seeding for Splitflask. Owner confirmed = advertising. ⚠️ TJ: 1099-NEC required if any individual received ≥$600/yr total; filed Sch C said "No" to 1099s — compliance item but does not affect deductibility.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Boardroom rental reimbursement Q1 2025 (C-corp governance meetings)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns RENT — 4/30/25 transfer, bank memo: "Boardroom Rental Reimbursement Q125" (reclassified 4D)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Owner transfer out $1,000 with explicit bank memo "Boardroom Rental Reimbursement Q125." Deductible rent for C-corp board/governance meetings. Keep meeting minutes on file. Source: S180 4/30/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Royceton corporate rental (Nov 2025)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SPLT_2025_Txns RENT — 11/19/25 transfer "Business Checking Balance" (reclassified 4D)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Transfer to Royceton $1,300, bank memo: "Business Checking Balance." Owner confirmed = SPLT warehouse/office rental, deductible. Source: S187 11/19/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Repairs &amp; maintenance — SPLT warehouse electrical (Frank, Sep 2025)</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B37" t="n">
         <v>251.1</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>SPLT_2025_Txns OPEX_REPAIRS — 2 Zelle payments to Frank 9/17/25 ($185 + $66.10) (reclassified 4D)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Zelle to Frank 9/17/25: $185.00 + $66.10 = $251.10. Owner confirmed = electrician, SPLT warehouse power fix. Repairs &amp; maintenance. Keep invoice on file. Source: S185.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="8" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Shopify Capital financing cost (interest portion)</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>TJ ITEM</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>⚠️ TJ EXTRACT</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>SPLT_2025_Txns DEBT_SHOPIFY_CAPITAL $4,237.64 total</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Total repaid $4,237.64. Split: PRINCIPAL non-deductible; INTEREST/fee portion = deductible. TJ: pull Shopify Capital agreement to state deductible financing cost. Do NOT deduct the full $4,237.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="22" t="inlineStr">
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>SECTION B SUBTOTAL — WF bank (excl. Shopify Capital; Assembly 4D final)</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B39" t="n">
         <v>182723.85</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1"/>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>NON-DEDUCTIBLE items excluded from Section B (in WF bank but removed): PERSONAL $52,999.90 (after 4D reclassifications: Venmo $1,011.65 + Boardroom $1,000 + Royceton $1,300 + Frank $251.10 reclassified OUT; Paris travel $418.53 reclassified IN from OPEX_TRAVEL) | DEBT_CHASE_PAYMENT $118,405.79 (balance sheet) | INTERCO_OUT_SGM $1,600.00 (balance sheet) | NON_REV_OWNER_LOAN $81,203.67 (not income) | NON_REV_REVERSAL $6.62. DEFERRED_KICKSTARTER $54,386.08 = INCOME (Fix 2). Tesla $6,159.15 stays PERSONAL (non-deductible, covered by standard mileage election). ATM cash $1,200 stays PERSONAL (owner draw, no receipt trail). Paris trip all items PERSONAL (retail $611.70 + hotel/flights $418.53 now reclassified here).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1"/>
     <row r="41" ht="8" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>NON-DEDUCTIBLE items excluded from Section B (in WF bank but removed): PERSONAL $52,999.90 (after 4D reclassifications: Venmo $1,011.65 + Boardroom $1,000 + Royceton $1,300 + Frank $251.10 reclassified OUT; Paris travel $418.53 reclassified IN from OPEX_TRAVEL) | DEBT_CHASE_PAYMENT $118,405.79 (balance sheet) | INTERCO_OUT_SGM $1,600.00 (balance sheet) | NON_REV_OWNER_LOAN $81,203.67 (not income) | NON_REV_REVERSAL $6.62. DEFERRED_KICKSTARTER $54,386.08 = INCOME (Fix 2). Tesla $6,159.15 stays PERSONAL (non-deductible, covered by standard mileage election). ATM cash $1,200 stays PERSONAL (owner draw, no receipt trail). Paris trip all items PERSONAL (retail $611.70 + hotel/flights $418.53 now reclassified here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1"/>
+    <row r="43" ht="8" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>SECTION C — Chase ···3247 Credit Card (charges on Chase, not WF bank)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Facebook ads — Chase ···3247 (stated from Meta invoice, Jan–Mar 2025 heavy)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B44" s="14" t="n">
         <v>51294.89</v>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>Facebook-Ads-Splitflask-2025-invoice (Meta invoice, card-coded)</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>Stated from Meta invoice. Card ···3247 = SPLT Chase card. Jan–Mar 2025 = Shark Tank airing period (heavy spend). SEPARATE from WF debit ···2100 (Section B) — no double-count. ⚠️ ASSEMBLY 4C FLAG: Bank total $22,351.63 vs Splitflask FB invoice ···2100 $21,216.81 = $1,134.82 delta. Per CLAUDE.md rule, bank is authoritative for debit cards. However, $1,134.82 is NOT on the Splitflask invoice and NOT on the CB invoice (CB invoice = ···3247 only). Owner: confirm which Meta ad account the extra $1,134.82 belongs to (2nd Meta account? period overlap?). If non-Splitflask: remove $1,134.82 → income +$69,990. Currently using bank figure pending ID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="8" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Veeqo shipping/fulfillment labels (all 9 stmts, Feb–Dec 2025)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>17592</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Chase ···3247 stmts (9 stmts, all foot)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Per-label shipping charges, hundreds of individual transactions. Shipping fulfillment is core COGS-adjacent cost. Stmts: Chase1–Chase10 (excl Chase7 dup). All statements foot to closing balance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Shopify subscriptions + apps (9 stmts)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>3844.68</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>SUBSTANTIATED</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Chase ···3247 stmts</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>⚠️ TJ: verify Shopify Capital repayment split (principal non-deductible, interest deductible). Charges range $12.99–$1,134/month; some may include Shopify Capital payments. Substantiated from card statements; TJ extracts capital vs fee component.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Klaviyo email marketing SaaS (9 stmts)</t>
+          <t>Veeqo shipping/fulfillment labels (all 9 stmts, Feb–Dec 2025)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4305</v>
+        <v>17592</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2795,23 +2776,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts</t>
+          <t>Chase ···3247 stmts (9 stmts, all foot)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Email marketing platform. Monthly subscription + usage charges. Nov/Dec had two charges ($385 + $640) = plan upgrade or overage mid-month. All deductible.</t>
+          <t>Per-label shipping charges, hundreds of individual transactions. Shipping fulfillment is core COGS-adjacent cost. Stmts: Chase1–Chase10 (excl Chase7 dup). All statements foot to closing balance.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PatentYogi patent drafting services (Mar, May, Jul stmts)</t>
+          <t>Shopify subscriptions + apps (9 stmts)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3942</v>
+        <v>3844.68</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2820,23 +2801,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (Chase2 $1,707 + Chase6 $362 + Chase4 $1,873)</t>
+          <t>Chase ···3247 stmts</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Patent drafting and prosecution services for Splitflask patent. Deductible as legal/professional fees for IP protection.</t>
+          <t>⚠️ TJ: verify Shopify Capital repayment split (principal non-deductible, interest deductible). Charges range $12.99–$1,134/month; some may include Shopify Capital payments. Substantiated from card statements; TJ extracts capital vs fee component.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Campaign services: Ecom Filmworks + Crowdfunding Pros + Hugebackers</t>
+          <t>Klaviyo email marketing SaaS (9 stmts)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3993</v>
+        <v>4305</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2845,23 +2826,23 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (Chase2, Chase6)</t>
+          <t>Chase ···3247 stmts</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ecom Filmworks $2,000 (video production for Splitflask content). Crowdfunding Pros $1,932 (Kickstarter campaign management). Hugebackers $61 (crowdfunding platform/consulting). All direct Splitflask marketing.</t>
+          <t>Email marketing platform. Monthly subscription + usage charges. Nov/Dec had two charges ($385 + $640) = plan upgrade or overage mid-month. All deductible.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chase Sapphire Reserve business card interest (Aug/Sep + Sep/Oct + Oct/Nov)</t>
+          <t>PatentYogi patent drafting services (Mar, May, Jul stmts)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1314</v>
+        <v>3942</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2870,23 +2851,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Chase stmts Chase1 $377.65 + Chase5 $464.99 + Chase3 $471.40</t>
+          <t>Chase ···3247 stmts (Chase2 $1,707 + Chase6 $362 + Chase4 $1,873)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Business card interest charged Aug/Sep, Sep/Oct, Oct/Nov statements. Paid in full Feb–Jul 2025 ($0 interest those months). Deductible under IRC §163 as business interest expense.</t>
+          <t>Patent drafting and prosecution services for Splitflask patent. Deductible as legal/professional fees for IP protection.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Chase Sapphire Reserve annual membership fee</t>
+          <t>Campaign services: Ecom Filmworks + Crowdfunding Pros + Hugebackers</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>550</v>
+        <v>3993</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2895,23 +2876,23 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chase8 (Feb/Mar 2025 first statement, Fees $550)</t>
+          <t>Chase ···3247 stmts (Chase2, Chase6)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Annual credit card membership fee on SPLT business card. Deductible as ordinary business expense. Charged in first statement (card opened Feb 2025).</t>
+          <t>Ecom Filmworks $2,000 (video production for Splitflask content). Crowdfunding Pros $1,932 (Kickstarter campaign management). Hugebackers $61 (crowdfunding platform/consulting). All direct Splitflask marketing.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IONOS web hosting + domains (all 9 stmts)</t>
+          <t>Chase Sapphire Reserve business card interest (Aug/Sep + Sep/Oct + Oct/Nov)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>876.5</v>
+        <v>1314</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2920,23 +2901,23 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (multiple charges/month)</t>
+          <t>Chase stmts Chase1 $377.65 + Chase5 $464.99 + Chase3 $471.40</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IONOS web hosting and domain registration. Monthly recurring service. Chase1 includes PayPal IONOS $323 (likely annual domain renewal). All deductible.</t>
+          <t>Business card interest charged Aug/Sep, Sep/Oct, Oct/Nov statements. Paid in full Feb–Jul 2025 ($0 interest those months). Deductible under IRC §163 as business interest expense.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Next Insurance — general liability (4 stmts: Aug–Dec)</t>
+          <t>Chase Sapphire Reserve annual membership fee</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>411.67</v>
+        <v>550</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2945,23 +2926,23 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts Chase1/3/5/9 (~$103/month)</t>
+          <t>Chase8 (Feb/Mar 2025 first statement, Fees $550)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Next Insurance general liability policy for Splitflask. Monthly premium $102.67–$103. Product liability / general commercial coverage. Deductible business insurance.</t>
+          <t>Annual credit card membership fee on SPLT business card. Deductible as ordinary business expense. Charged in first statement (card opened Feb 2025).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fiverr freelance services (Feb/Mar, Mar/Apr, Jun/Jul stmts)</t>
+          <t>IONOS web hosting + domains (all 9 stmts)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>713</v>
+        <v>876.5</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2970,23 +2951,23 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (Chase8 $449 + Chase2 $198 + Chase4 $66)</t>
+          <t>Chase ···3247 stmts (multiple charges/month)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Freelance contractors via Fiverr for creative/design/content work. Business purpose: Splitflask product photography, marketing assets.</t>
+          <t>IONOS web hosting and domain registration. Monthly recurring service. Chase1 includes PayPal IONOS $323 (likely annual domain renewal). All deductible.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Adv Specialty — promotional/brand materials (Aug/Sep, Sep/Oct)</t>
+          <t>Next Insurance — general liability (4 stmts: Aug–Dec)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>596</v>
+        <v>411.67</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2995,23 +2976,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Chase stmts Chase1 $298 + Chase5 $298</t>
+          <t>Chase ···3247 stmts Chase1/3/5/9 (~$103/month)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Promotional merchandise/materials for Splitflask brand. $298 × 2 statements.</t>
+          <t>Next Insurance general liability policy for Splitflask. Monthly premium $102.67–$103. Product liability / general commercial coverage. Deductible business insurance.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI tools + SaaS: OpenAI, Claude.ai, QuickBooks, LinkedIn, Reddit/TikTok Ads, GoDaddy + misc</t>
+          <t>Fiverr freelance services (Feb/Mar, Mar/Apr, Jun/Jul stmts)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1723.77</v>
+        <v>713</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3020,73 +3001,73 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts (itemized in each stmt)</t>
+          <t>Chase ···3247 stmts (Chase8 $449 + Chase2 $198 + Chase4 $66)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OpenAI ChatGPT $175.01 (AI tool for business). Claude.ai $100 (AI assistant). QuickBooks $50. LinkedIn $45 (professional marketing). Reddit Ads $209. TikTok Ads $120. GoDaddy $133 (domain). Google Workspace $23.76 (flag TJ: Cyberbrands account on SPLT card). DMVerify $14 (mailing list verification). US Patent USPTO $65 (filing fee). AMZ Amazon Payments + Sponsored $134.93. Alibaba $134 (supplies/COGS). Staples $9.60. Hugebackers already above. Total miscellaneous SaaS/tools/ads: $1,723.77.</t>
+          <t>Freelance contractors via Fiverr for creative/design/content work. Business purpose: Splitflask product photography, marketing assets.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CGL Los Angeles — legal/logistics services</t>
+          <t>Adv Specialty — promotional/brand materials (Aug/Sep, Sep/Oct)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3195</v>
+        <v>596</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SUBSTANTIATED (owner confirmed)</t>
+          <t>SUBSTANTIATED</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmts Chase8 $2,775 + Chase2 $420 (4D: owner confirmed business)</t>
+          <t>Chase stmts Chase1 $298 + Chase5 $298</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CGL Los Angeles. Owner confirmed = SPLT legal expenses (formation/contracts/IP). Two charges: Chase8 $2,775 + Chase2 $420 = $3,195. Deductible as legal/professional fees.</t>
+          <t>Promotional merchandise/materials for Splitflask brand. $298 × 2 statements.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Foremost Insurance — property/warehouse insurance</t>
+          <t>AI tools + SaaS: OpenAI, Claude.ai, QuickBooks, LinkedIn, Reddit/TikTok Ads, GoDaddy + misc</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1735</v>
+        <v>1723.77</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUBSTANTIATED (owner confirmed)</t>
+          <t>SUBSTANTIATED</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmt Chase2 (4D: confirmed PROPERTY insurance, not vehicle)</t>
+          <t>Chase ···3247 stmts (itemized in each stmt)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Foremost Insurance $1,735. RESOLVED: property/warehouse/premises insurance, NOT vehicle insurance. Standard mileage bar does NOT apply. Deductible as business insurance. Source: Chase2.</t>
+          <t>OpenAI ChatGPT $175.01 (AI tool for business). Claude.ai $100 (AI assistant). QuickBooks $50. LinkedIn $45 (professional marketing). Reddit Ads $209. TikTok Ads $120. GoDaddy $133 (domain). Google Workspace $23.76 (flag TJ: Cyberbrands account on SPLT card). DMVerify $14 (mailing list verification). US Patent USPTO $65 (filing fee). AMZ Amazon Payments + Sponsored $134.93. Alibaba $134 (supplies/COGS). Staples $9.60. Hugebackers already above. Total miscellaneous SaaS/tools/ads: $1,723.77.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Paddle.net STOCKLMTS — software subscription</t>
+          <t>CGL Los Angeles — legal/logistics services</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>432</v>
+        <v>3195</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3095,23 +3076,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmt Chase6 (4D: owner confirmed business software)</t>
+          <t>Chase ···3247 stmts Chase8 $2,775 + Chase2 $420 (4D: owner confirmed business)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paddle.net STOCKLMTS $432. Owner confirmed = business software subscription. Deductible.</t>
+          <t>CGL Los Angeles. Owner confirmed = SPLT legal expenses (formation/contracts/IP). Two charges: Chase8 $2,775 + Chase2 $420 = $3,195. Deductible as legal/professional fees.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SW Airlines — business travel (Las Vegas, business purpose)</t>
+          <t>Foremost Insurance — property/warehouse insurance</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>186</v>
+        <v>1735</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3120,23 +3101,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmt Chase2 (4D: owner confirmed business travel)</t>
+          <t>Chase ···3247 stmt Chase2 (4D: confirmed PROPERTY insurance, not vehicle)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SW Airlines Las Vegas $186. Owner confirmed business trip (tradeshow/supplier/meeting). Deductible travel. Document business purpose.</t>
+          <t>Foremost Insurance $1,735. RESOLVED: property/warehouse/premises insurance, NOT vehicle insurance. Standard mileage bar does NOT apply. Deductible as business insurance. Source: Chase2.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Merchant D24939973 FL — misc business expense</t>
+          <t>Paddle.net STOCKLMTS — software subscription</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>57</v>
+        <v>432</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3145,23 +3126,23 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmt Chase4 (4D: owner confirmed business)</t>
+          <t>Chase ···3247 stmt Chase6 (4D: owner confirmed business software)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Unknown FL merchant D24939973 $57. Owner confirmed = SPLT business expense. Deductible. Owner to identify vendor for records.</t>
+          <t>Paddle.net STOCKLMTS $432. Owner confirmed = business software subscription. Deductible.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Safety First Driving — business safety training</t>
+          <t>SW Airlines — business travel (Las Vegas, business purpose)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>475</v>
+        <v>186</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3170,286 +3151,332 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Chase ···3247 stmt Chase6 (4D: owner confirmed business)</t>
+          <t>Chase ···3247 stmt Chase2 (4D: owner confirmed business travel)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Safety First Driving $475. Owner confirmed = SPLT business expense (safety training/certification). Deductible.</t>
+          <t>SW Airlines Las Vegas $186. Owner confirmed business trip (tradeshow/supplier/meeting). Deductible travel. Document business purpose.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Merchant D24939973 FL — misc business expense</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>57</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmt Chase4 (4D: owner confirmed business)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Unknown FL merchant D24939973 $57. Owner confirmed = SPLT business expense. Deductible. Owner to identify vendor for records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Safety First Driving — business safety training</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>475</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED (owner confirmed)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Chase ···3247 stmt Chase6 (4D: owner confirmed business)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Safety First Driving $475. Owner confirmed = SPLT business expense (safety training/certification). Deductible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Facebook ads — Meta ···0566 MasterCard (SPLT expense)</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B63" t="n">
         <v>3070</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>SUBSTANTIATED (owner confirmed)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Meta FB invoice 2025, card ···0566 MasterCard (4D: owner confirmed SPLT expense)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>···0566 MasterCard $3,069.79 ≈ $3,070. Identified from Meta FB invoice 2025. Owner confirmed = SPLT advertising expense. Source: Facebook-Ads-Splitflask-2025-invoice card ···0566. ⚠️ TJ: confirm ···0566 card identity and ensure bank statement from that card is on file.</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="22" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
         <is>
           <t>SECTION C SUBTOTAL — Chase ···3247 + ···0566 confirmed (Assembly 4D final)</t>
         </is>
       </c>
-      <c r="B65" s="23" t="n">
+      <c r="B67" s="23" t="n">
         <v>99796.03999999999</v>
       </c>
-      <c r="C65" s="22" t="inlineStr">
+      <c r="C67" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D65" s="22" t="inlineStr">
+      <c r="D67" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="22">
+      <c r="E67" s="22">
         <f> FB ads $51,294.89 + non-FB business $39,351.15. FB: Meta invoice card-coded (SUBSTANTIATED). Non-FB: 9 Chase stmts, all foot to closing balances. Prior "~$67K DROPPED" line RETIRED — now fully substantiated.</f>
         <v/>
       </c>
     </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>TOTAL SUBSTANTIATED DEDUCTIONS (Assembly 4D — LOCKED FINAL)</t>
         </is>
       </c>
-      <c r="B67" s="24" t="n">
-        <v>382529.81</v>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B69" s="24" t="n">
+        <v>385273.88</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E67" s="3">
+      <c r="E69" s="3">
         <f> Section A $100,010 + Section B $179,580 + Section C $90,646</f>
         <v/>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="22" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
         <is>
           <t>FILED-VS-BANK ANALYSIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>Filed gross receipts (estimated)</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>$369,980.87</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>All WF bank credits (bank-feed based)</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Estimated from 3-way match: credits $369,981 − debits $360,131 = closing balance $9,850.39</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>ESTIMATE — TJ must confirm from actual filed 1120</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Filed deductions (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ TJ must provide</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Filed 1120 deduction schedule</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>NOT in source docs this session</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>⚠️ CRITICAL: unlike CB 2024 (QB P&amp;L available), no filed deduction detail available. If filed deducted bank debits incl. personal $56K + Chase payments $118K + interco $1.6K → over-deduction $176K (same CB-2024 pattern). TJ provides filed 1120 Part II/III deduction detail.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>Filed net income (estimated)</t>
+          <t>Filed gross receipts (estimated)</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>~$9,850 est.</t>
+          <t>$369,980.87</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Three-way bank match</t>
+          <t>All WF bank credits (bank-feed based)</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Credits $369,981 − debits $360,131 = $9,850</t>
+          <t>Estimated from 3-way match: credits $369,981 − debits $360,131 = closing balance $9,850.39</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>ESTIMATE only — equals closing bank balance. Real filed taxable income may differ significantly based on actual deductions claimed.</t>
+          <t>ESTIMATE — TJ must confirm from actual filed 1120</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>Amended gross receipts</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>$456,722.11</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>Platform-gross basis</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>See Tab 3</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>Increase from filed: Amazon nominee + TikTok gross + other channels. Fix 2: Kickstarter $54,386 now income (cash-basis C-corp). Fix 3: BNPL $9,063 removed (inside Shopify 1099-K). Amazon CA/MX kept.</t>
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Filed deductions (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ TJ must provide</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Filed 1120 deduction schedule</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>NOT in source docs this session</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>⚠️ CRITICAL: unlike CB 2024 (QB P&amp;L available), no filed deduction detail available. If filed deducted bank debits incl. personal $56K + Chase payments $118K + interco $1.6K → over-deduction $176K (same CB-2024 pattern). TJ provides filed 1120 Part II/III deduction detail.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
+          <t>Filed net income (estimated)</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>~$9,850 est.</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Three-way bank match</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Credits $369,981 − debits $360,131 = $9,850</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>ESTIMATE only — equals closing bank balance. Real filed taxable income may differ significantly based on actual deductions claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Amended gross receipts</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>$456,722.11</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Platform-gross basis</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>See Tab 3</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>Increase from filed: Amazon nominee + TikTok gross + other channels. Fix 2: Kickstarter $54,386 now income (cash-basis C-corp). Fix 3: BNPL $9,063 removed (inside Shopify 1099-K). Amazon CA/MX kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
           <t>Amended deductions</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>$382,529.81</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Assembly 4D final — Section B +$3,144 + Section C +$9,150 = +$12,294 new deductions</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>See above</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>Fix 1: Chase non-FB $39,351 added (9 stmts, all foot). Adds: platform fees $100K + Chase FB $51K + Chase non-FB $39K. Removes: personal $56K + Chase payments $118K (balance sheet).</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Amended net income (FINAL — Assembly 4D LOCKED)</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>~$56,561</t>
         </is>
       </c>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Amendment waterfall</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>ASSEMBLY 4D LOCKED: $56,561 (~$11,878 @ 21% corp rate). Waterfall from Assembly 4C: $68,855 (base) → −$6,080 (6 Chase flagged items confirmed business) → −$3,070 (···0566 confirmed SPLT) → −$3,144 (personal-bucket reclassifications: Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251; net of Paris travel $419 removed). = $56,561. Corp tax: ~$11,878 @ 21%. Still COMPLIANCE-DRIVEN. ⚠️ TJ items: Shopify Capital interest (additive, lowers profit further); COGS method; Augusta 14-day cap; $148K loan-vs-capital. ⚠️ 1099-NEC: Venmo influencer payments (19 × $44–$65 = $1,012) — confirm no individual ≥$600/yr.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>⚠️ Non-deductibles in WF debits (if filed on bank-feed)</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>$56,144 personal + $118,406 Chase payments + $1,600 interco</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>If filed deducted these</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>WF bank classification</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>If filed return used all bank debits as deductions → over-deduction ~$176K. Amendment corrects by removing these AND adding legitimate platform fees + Chase FB ads. Net effect depends on actual filed numbers — TJ confirms.</t>
         </is>
@@ -3495,7 +3522,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
         <is>

--- a/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SPLT_2025_Amendment_Packet.xlsx
@@ -596,7 +596,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -954,7 +953,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29">
         <f>== ASSEMBLY 4C VERIFICATION FINDINGS (2026-07-11) ===</f>
@@ -1692,7 +1690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1714,6 +1712,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1856,6 +1855,173 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Related-party transaction. Pass-through / net-zero per CLAUDE.md. Not product COGS. Invoice + completion acknowledgment must be on file. Confirm arm's-length terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ATLANTIC ACCESS — CONSIGNMENT SELL-THROUGH (INV-8707, Feb–Aug 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Units sold through Atlantic Access (est.)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>~63 units</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£2,529.86 net revenue ÷ ~£37 est. UK price. Source: INV-8707. Exact count needs AA sales report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Remaining at Atlantic Access (on consignment)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>~1,337 units</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1,400 consigned − 63 sold = 1,337 remaining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Updated ending inventory (total)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>~3,693 units</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3,756 prior − 63 Atlantic sell-through = 3,693.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ending inventory split:</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  US warehouse</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>~2,356 units</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Owner-confirmed. 3,756 − 1,400 consigned = 2,356 domestic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  At Atlantic Access (UK consignment)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>~1,337 units</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Title retained by SPLT (agent structure, INV-8707). Disclosed on balance sheet as inventory asset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Inventory value @ landed cost $8.11/unit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$29,950</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3,693 × $8.113 = $29,950. Landed: ($103,463 factory + $18,235 freight) ÷ 15,000 = $8.11/unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CASH BASIS P&amp;L IMPACT 2025: $0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No cash received from Atlantic + no payment to Atlantic in 2025 (confirmed vs SPLT WF …0423 bank, all 12 months). Revenue and deduction both recognized when cash moves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BALANCE SHEET PAYABLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$1,769</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£1,370.35 × 1.29 GBP/USD = $1,769. Outstanding payable to Atlantic Access Ltd as of 12/31/25. Invoice INV-8707, due 31 Aug 2025 — UNPAID. Disclosure item on SPLT 2025 Schedule L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LANDED COST NOTE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>$8.113/unit</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Factory (Kangdao wires) $103,463 ÷ 15,000 = $6.897 + freight $18,235 ÷ 15,000 = $1.216 = $8.113 landed. Atlantic Access contract Cl. 3.2: agent pays UK import duties (deducted from sums owed SPLT) — no additional UK duty cost to SPLT.</t>
         </is>
       </c>
     </row>
